--- a/ksoft/docs/records/Item_Family_Stock_Records.xlsx
+++ b/ksoft/docs/records/Item_Family_Stock_Records.xlsx
@@ -3349,13 +3349,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887AC114-F4E4-4B8D-9CF4-1A2793DB52B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70563DB1-5BB3-4833-81CD-759216D88C2D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0969BA8C-5D89-4811-8D28-7103A6321E2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB41649F-B355-4640-9895-2C3723BD99DC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CB9AE20-5512-4FC3-ADA1-3C0682D74DBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B0DBE5F-5A2B-47A2-8756-7F2FF7802FC7}"/>
 </file>
--- a/ksoft/docs/records/Item_Family_Stock_Records.xlsx
+++ b/ksoft/docs/records/Item_Family_Stock_Records.xlsx
@@ -3349,13 +3349,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70563DB1-5BB3-4833-81CD-759216D88C2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887AC114-F4E4-4B8D-9CF4-1A2793DB52B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB41649F-B355-4640-9895-2C3723BD99DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0969BA8C-5D89-4811-8D28-7103A6321E2D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B0DBE5F-5A2B-47A2-8756-7F2FF7802FC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CB9AE20-5512-4FC3-ADA1-3C0682D74DBF}"/>
 </file>